--- a/base_datos_vsp_sucre.xlsx
+++ b/base_datos_vsp_sucre.xlsx
@@ -22,6 +22,11 @@
     <sheet name="Brotes_ERI" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Tablero_Problemas" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Auditoria_Logs" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Consecutivos_Actas" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Casos_Criticos" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="IPS_UPGD" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Boletines_Data" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Muestras_Lab" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -539,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -586,53 +591,6 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Ruta_Documento</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Historia Clínica</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>JUAN CARLOS GARCIA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>C.C. 1102837548</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>COOSALUD</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Coveñas</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ADMINISTRADOR PRINCIPAL</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>🟢 RECIBIDO</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>soportes_compromisos\HC_0_202606071314.pdf</t>
         </is>
       </c>
     </row>
@@ -805,7 +763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1003,6 +961,625 @@
       <c r="D9" t="inlineStr">
         <is>
           <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-08 08:06:46</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-08 08:10:21</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Cierre de sesión manual</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-08 08:10:33</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-08 08:29:51</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-08 08:39:18</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-08 08:41:24</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Cierre de sesión manual</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-08 08:45:39</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-08 09:45:03</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-08 10:22:13</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-08 10:24:39</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-08 10:58:59</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-08 11:10:12</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-08 11:58:05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-08 12:48:35</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-08 12:54:03</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-08 13:23:29</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-08 13:34:42</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-08 14:20:33</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-08 14:57:24</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Tipo_Documento</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Consecutivo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Asunto</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ACTA (Reuniones/Comités)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ACTA-VSP-2026-001</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>DFDDFDF</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>EDER JESUS PATERNINA RODRIGUEZ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fecha_Notificacion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Evento</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Identificacion</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Fase</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Dias_Mora</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Nombre_IPS</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Codigo_Sede</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reporto_Ultima_Semana</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Fecha_Ultimo_Reporte</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Semana</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Evento</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Edad</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Sexo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Casos</t>
         </is>
       </c>
     </row>
@@ -1079,6 +1656,62 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fecha_Envio</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Paciente_Identificacion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Tipo_Muestra</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Evento_Sospechoso</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Dias_Espera</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1815,7 +2448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1869,33 +2502,6 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>🏠 Inicio,📝 Registrar Actividad,🛡️ Disponibilidad Semanal,📋 Compromisos Técnicos,🛠️ Enlaces y Solicitudes HC,📄 Actas e Informes,🚨 Alertas e Inventario,🔍 Filtros y Dashboard,🚨 Brotes y ERI,🛑 Tablero de Problemas,🏘️ Vigilancia Comunitaria (VBC),📈 Tableros SIVIGILA,🛡️ Calidad del Dato,📞 Directorio de Red,🤖 Asistente Redactor VSP,⚙️ Panel Maestro y Roles,🛡️ Auditoría y Logs</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ana karina</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1102837548</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ANA KARINA PEÑATES</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Apoyo</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>🏠 Inicio,📝 Registrar Actividad,🛠️ Enlaces y Solicitudes HC,📄 Actas e Informes,🚨 Alertas e Inventario,📞 Directorio de Red</t>
         </is>
       </c>
     </row>

--- a/base_datos_vsp_sucre.xlsx
+++ b/base_datos_vsp_sucre.xlsx
@@ -27,6 +27,8 @@
     <sheet name="IPS_UPGD" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="Boletines_Data" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="Muestras_Lab" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Riesgos_VSP" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Cumpleanos" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -544,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -593,6 +595,49 @@
           <t>Ruta_Documento</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Historia Clínica</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>JUAN JOSE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>C.C. 1102883838939</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>COOSALUD</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Caimito</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>🔴 PENDIENTE</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -656,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -700,6 +745,84 @@
           <t>Ruta_ERI</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SINCELEJO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Síndrome Febril (Posible Dengue/Malaria/Zika/Chikungunya) (Desde VBC)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Alerta Comunitaria: Presidente Junta Acción Comunal</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Hay 15 personas con fiebre altísima y dolor en los huesos en la misma cuadra.
+[Inv. Campo]: Visita de campo</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>🔴 ACTIVO</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TOLU</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Zoonosis / Animales Enfermos / Mordeduras (Desde VBC)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Alerta Comunitaria: Policía Ambiental</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Perro callejero con salivación excesiva mordió a 3 turistas.
+[Inv. Campo]: Visita Campo</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>🔴 ACTIVO</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -763,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1377,6 +1500,1480 @@
         </is>
       </c>
       <c r="D28" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-08 21:52:45</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-08 21:59:32</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:02:51</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:33:42</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-09 06:46:59</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-09 06:49:55</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-06-09 06:59:15</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-06-09 19:44:48</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-06-09 20:49:07</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-06-09 20:52:09</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-09 21:12:28</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-09 21:14:58</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-09 21:22:01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-09 21:37:19</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-09 21:56:05</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-09 21:58:59</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:04:22</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:09:52</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:39</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:17:55</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:44:05</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:46:52</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:53:51</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:56:45</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:58:51</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-06-09 23:04:08</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-06-09 23:10:29</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-06-09 23:15:59</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-06-09 23:22:35</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-06-09 23:42:05</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-06-09 23:45:42</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-06-09 23:56:35</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:55</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:11:00</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:20:41</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:32:03</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:47:54</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:50:03</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:58:50</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-06-10 20:15:49</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-06-10 20:19:56</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-06-10 20:46:41</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-06-10 20:50:44</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-06-10 20:53:15</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Verificación VBC 0 actualizada a: 🟢 Confirmado - Brote Activo</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Vigilancia Comunitaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-06-10 20:53:16</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Alerta VBC escalada automáticamente a Brotes ERI</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Vigilancia Comunitaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-06-10 21:02:17</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-06-10 21:08:44</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-06-10 21:19:48</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-06-10 21:22:05</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Verificación VBC 2 actualizada a: 🟢 Confirmado - Brote Activo</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Vigilancia Comunitaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-06-10 21:22:05</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Alerta VBC escalada automáticamente a Brotes ERI</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Vigilancia Comunitaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-06-10 21:26:40</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-06-10 21:45:00</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-06-10 21:58:57</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:36</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:07:11</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:14:10</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:21:03</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:43:32</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:55:19</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-06-10 23:17:30</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:03:00</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:05:24</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:18:51</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:22:23</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:33:01</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:36:19</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Autenticación</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:45:24</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>JUAN GARCIA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Inicio de sesión exitoso</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
         <is>
           <t>Autenticación</t>
         </is>
@@ -1712,6 +3309,194 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fecha_Registro</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Probabilidad</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Impacto</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Nivel_Riesgo</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Mitigacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Biológico / Epidemiológico</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Fenomeno del Niño</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Seleccione...</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Alto 🟠</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>HECTOR FABIO RENTERIA</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Cerrado/Controlado</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Sin acciones registradas aún.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Biológico / Epidemiológico</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>fenomeno del niño</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Buenavista</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Extremo 🔴</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>MARLON ESPITIA CERPA</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Cerrado/Controlado</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Sin acciones registradas aún.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Funcionario</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Fecha_Nacimiento</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2407,7 +4192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2434,6 +4219,33 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>Enlace_Formulario</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CAPACITACION</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SIVIGILA (11-06-2026)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ANA LUCIA MENDOZA TAMARA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSc1o7tjgmWqKhdTV1HuYTqJkSa3KPHI2BWQNrJ3zT9zndvX6A/viewform?usp=pp_url&amp;entry.67209856=SIVIGILA%20%2811-06-2026%29</t>
         </is>
       </c>
     </row>
@@ -2516,7 +4328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2560,6 +4372,160 @@
           <t>Responsable_Verificacion</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Resultado_Investigacion</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Ruta_Soporte_VBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SINCELEJO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Barrio La Sabana</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Síndrome Febril (Posible Dengue/Malaria/Zika/Chikungunya)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Presidente Junta Acción Comunal</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Hay 15 personas con fiebre altísima y dolor en los huesos en la misma cuadra.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>🟢 Confirmado - Brote Activo</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Andrés Pérez</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Visita de campo</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>COROZAL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Vereda Las Palmas</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Enfermedad Diarreica Aguda (EDA)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Docente Rural</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8 niños del colegio amanecieron con vómito y diarrea tras tomar agua del pozo.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>🟡 Descartado / Falsa Alarma</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>María Gómez</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Visita realizada. Fue por un jugo en mal estado, no es brote.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TOLU</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sector Playa</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Zoonosis / Animales Enfermos / Mordeduras</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Policía Ambiental</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Perro callejero con salivación excesiva mordió a 3 turistas.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>🟢 Confirmado - Brote Activo</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Juan Díaz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Visita Campo</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
